--- a/garch_forecast_results.xlsx
+++ b/garch_forecast_results.xlsx
@@ -447,541 +447,541 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.009536444633824342</v>
+        <v>0.009536444633824163</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01051329051141209</v>
+        <v>0.0105132905114119</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01216047828930611</v>
+        <v>0.01215782614303152</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.00960605366832824</v>
+        <v>0.009606053668328231</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01071359385807381</v>
+        <v>0.01071359385807423</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01220352914273318</v>
+        <v>0.01220063076315248</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.009673784596870676</v>
+        <v>0.009673784596870502</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01089071750722089</v>
+        <v>0.01089071750722112</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01224557228007232</v>
+        <v>0.01224243407518852</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.009739703962661959</v>
+        <v>0.009739703962662079</v>
       </c>
       <c r="B5" t="n">
         <v>0.01104770106940656</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01228663511423455</v>
+        <v>0.01228326327972922</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.009803874946313551</v>
+        <v>0.009803874946313816</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01118710297510595</v>
+        <v>0.01118710297510575</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01232674411436252</v>
+        <v>0.01232314464306545</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.009866357603063791</v>
+        <v>0.009866357603064082</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01131109586596871</v>
+        <v>0.01131109586596863</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01236592484899235</v>
+        <v>0.01236210353978964</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.009927209078362588</v>
+        <v>0.009927209078362769</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01142153863485837</v>
+        <v>0.01142153863485811</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01240420202664524</v>
+        <v>0.01240016449287902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.009986483804210113</v>
+        <v>0.009986483804210404</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01152003187611849</v>
+        <v>0.01152003187611852</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01244159953404097</v>
+        <v>0.01243735121142434</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0100442336783367</v>
+        <v>0.01004423367833642</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0116079612830015</v>
+        <v>0.01160796128300137</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01247814047210347</v>
+        <v>0.01247368662619406</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.01010050822804539</v>
+        <v>0.0101005082280455</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01168653211339747</v>
+        <v>0.01168653211339777</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01251384718991622</v>
+        <v>0.01250919292317614</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.01015535476031549</v>
+        <v>0.01015535476031589</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01175679691902587</v>
+        <v>0.01175679691902559</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01254874131677266</v>
+        <v>0.0125438915752447</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.01020881849956905</v>
+        <v>0.01020881849956901</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01181967811280874</v>
+        <v>0.01181967811280899</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01258284379245242</v>
+        <v>0.01257780337207345</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.01026094271433521</v>
+        <v>0.01026094271433552</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01187598652432665</v>
+        <v>0.01187598652432689</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01261617489584588</v>
+        <v>0.01261094844843112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.01031176883390429</v>
+        <v>0.0103117688339046</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01192643679666817</v>
+        <v>0.01192643679666842</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01264875427203937</v>
+        <v>0.01264334631094972</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.01036133655593693</v>
+        <v>0.01036133655593663</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01197166026723864</v>
+        <v>0.01197166026723896</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01268060095796034</v>
+        <v>0.01267501586347927</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.01040968394588388</v>
+        <v>0.01040968394588401</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01201221582291601</v>
+        <v>0.01201221582291591</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01271173340668211</v>
+        <v>0.01270597543112081</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.0104568475289795</v>
+        <v>0.0104568475289798</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01204859910843803</v>
+        <v>0.01204859910843783</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01274216951047023</v>
+        <v>0.01273624278301202</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.01050286237548653</v>
+        <v>0.01050286237548681</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01208125038409091</v>
+        <v>0.0120812503840908</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01277192662265434</v>
+        <v>0.01276583515396522</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.01054776217979781</v>
+        <v>0.01054776217979771</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01211056126649401</v>
+        <v>0.01211056126649421</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01280102157839947</v>
+        <v>0.01279476926501024</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.01059157933393871</v>
+        <v>0.01059157933393881</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01213688053890186</v>
+        <v>0.01213688053890193</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01282947071444385</v>
+        <v>0.01282306134291896</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.01063434499595419</v>
+        <v>0.01063434499595451</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01216051918101823</v>
+        <v>0.01216051918101814</v>
       </c>
       <c r="C22" t="n">
-        <v>0.01285728988786872</v>
+        <v>0.01285072713878196</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.01067608915361916</v>
+        <v>0.01067608915361936</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01218175474002822</v>
+        <v>0.01218175474002823</v>
       </c>
       <c r="C23" t="n">
-        <v>0.01288449449395801</v>
+        <v>0.01287778194567617</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.0107168406838626</v>
+        <v>0.01071684068386249</v>
       </c>
       <c r="B24" t="n">
-        <v>0.01220083514237791</v>
+        <v>0.01220083514237789</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01291109948320377</v>
+        <v>0.01290424061549922</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.01075662740826152</v>
+        <v>0.01075662740826122</v>
       </c>
       <c r="B25" t="n">
-        <v>0.01221798202829027</v>
+        <v>0.01221798202828988</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01293711937750652</v>
+        <v>0.01293011757499942</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.01079547614492289</v>
+        <v>0.0107954761449226</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01223339367702177</v>
+        <v>0.0122333936770218</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01296256828561995</v>
+        <v>0.01295542684106873</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.01083341275704356</v>
+        <v>0.01083341275704396</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01224724757962501</v>
+        <v>0.01224724757962494</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01298745991788189</v>
+        <v>0.01298018203532439</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.01087046219840989</v>
+        <v>0.01087046219840992</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01225970270688256</v>
+        <v>0.01225970270688265</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01301180760027332</v>
+        <v>0.01300439639802926</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.01090664855607303</v>
+        <v>0.01090664855607313</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0122709015126583</v>
+        <v>0.01227090151265782</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01303562428784354</v>
+        <v>0.01302808280138705</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.01094199509041895</v>
+        <v>0.01094199509041928</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01228097170682751</v>
+        <v>0.01228097170682734</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01305892257753746</v>
+        <v>0.01305125376224254</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.0109765242728262</v>
+        <v>0.01097652427282589</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01229002782691591</v>
+        <v>0.01229002782691583</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01308171472045703</v>
+        <v>0.01307392145423093</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.01101025782109209</v>
+        <v>0.01101025782109175</v>
       </c>
       <c r="B32" t="n">
-        <v>0.01229817263340693</v>
+        <v>0.01229817263340717</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01310401263358862</v>
+        <v>0.01309609771938845</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.01104321673279077</v>
+        <v>0.01104321673279075</v>
       </c>
       <c r="B33" t="n">
-        <v>0.01230549835018302</v>
+        <v>0.01230549835018342</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01312582791102525</v>
+        <v>0.01311779407927347</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.01107542131671157</v>
+        <v>0.01107542131671133</v>
       </c>
       <c r="B34" t="n">
-        <v>0.01231208776864209</v>
+        <v>0.01231208776864186</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0131471718347108</v>
+        <v>0.01313902174560988</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.0111068912225137</v>
+        <v>0.01110689122251393</v>
       </c>
       <c r="B35" t="n">
-        <v>0.01231801523155266</v>
+        <v>0.01231801523155303</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01316805538473008</v>
+        <v>0.01315979163048207</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.01113764546872427</v>
+        <v>0.01113764546872395</v>
       </c>
       <c r="B36" t="n">
-        <v>0.012323347510621</v>
+        <v>0.01232334751062099</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01318848924917213</v>
+        <v>0.01318011435611025</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.01116770246919176</v>
+        <v>0.01116770246919209</v>
       </c>
       <c r="B37" t="n">
-        <v>0.0123281445899481</v>
+        <v>0.01232814458994764</v>
       </c>
       <c r="C37" t="n">
-        <v>0.01320848383358363</v>
+        <v>0.0132000002642154</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.01119708005810264</v>
+        <v>0.01119708005810297</v>
       </c>
       <c r="B38" t="n">
-        <v>0.01233246036603705</v>
+        <v>0.01233246036603704</v>
       </c>
       <c r="C38" t="n">
-        <v>0.01322804927003943</v>
+        <v>0.01321945942501423</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.0112257955136554</v>
+        <v>0.011225795513655</v>
       </c>
       <c r="B39" t="n">
-        <v>0.01233634327368969</v>
+        <v>0.01233634327368962</v>
       </c>
       <c r="C39" t="n">
-        <v>0.01324719542584405</v>
+        <v>0.01323850164583924</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.01125386558048321</v>
+        <v>0.01125386558048333</v>
       </c>
       <c r="B40" t="n">
-        <v>0.01233983684600529</v>
+        <v>0.0123398368460053</v>
       </c>
       <c r="C40" t="n">
-        <v>0.01326593191188606</v>
+        <v>0.01325713647942132</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.01128130649090645</v>
+        <v>0.01128130649090624</v>
       </c>
       <c r="B41" t="n">
-        <v>0.01234298021571456</v>
+        <v>0.01234298021571462</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01328426809066297</v>
+        <v>0.01327537323184795</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.01130813398509071</v>
+        <v>0.01130813398509098</v>
       </c>
       <c r="B42" t="n">
-        <v>0.01234580856423048</v>
+        <v>0.0123458085642305</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01330221308398917</v>
+        <v>0.01329322097020006</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.01133436333017978</v>
+        <v>0.01133436333017984</v>
       </c>
       <c r="B43" t="n">
-        <v>0.01234835352406261</v>
+        <v>0.01234835352406252</v>
       </c>
       <c r="C43" t="n">
-        <v>0.01331977578040742</v>
+        <v>0.01331068852990421</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.01136000933846893</v>
+        <v>0.01136000933846922</v>
       </c>
       <c r="B44" t="n">
-        <v>0.012350643539591</v>
+        <v>0.01235064353959103</v>
       </c>
       <c r="C44" t="n">
-        <v>0.01333696484231283</v>
+        <v>0.01332778452179511</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.01138508638467872</v>
+        <v>0.01138508638467827</v>
       </c>
       <c r="B45" t="n">
-        <v>0.01235270419063416</v>
+        <v>0.01235270419063413</v>
       </c>
       <c r="C45" t="n">
-        <v>0.01335378871280832</v>
+        <v>0.01334451733891454</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.01140960842238256</v>
+        <v>0.01140960842238279</v>
       </c>
       <c r="B46" t="n">
-        <v>0.01235455848274958</v>
+        <v>0.01235455848274974</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0133702556222999</v>
+        <v>0.01336089516305105</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.0114335889996419</v>
+        <v>0.01143358899964206</v>
       </c>
       <c r="B47" t="n">
-        <v>0.01235622710776784</v>
+        <v>0.01235622710776794</v>
       </c>
       <c r="C47" t="n">
-        <v>0.01338637359484671</v>
+        <v>0.01337692597103804</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.01145704127389514</v>
+        <v>0.01145704127389497</v>
       </c>
       <c r="B48" t="n">
-        <v>0.01235772867767867</v>
+        <v>0.0123577286776783</v>
       </c>
       <c r="C48" t="n">
-        <v>0.01340215045427496</v>
+        <v>0.01339261754082025</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.01147997802614438</v>
+        <v>0.01147997802614463</v>
       </c>
       <c r="B49" t="n">
-        <v>0.0123590799346478</v>
+        <v>0.01235907993464746</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0134175938300697</v>
+        <v>0.01340797745729458</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.01150241167448174</v>
+        <v>0.0115024116744814</v>
       </c>
       <c r="B50" t="n">
-        <v>0.01236029593964449</v>
+        <v>0.01236029593964401</v>
       </c>
       <c r="C50" t="n">
-        <v>0.01343271116305088</v>
+        <v>0.01342301311794032</v>
       </c>
     </row>
     <row r="51">
@@ -989,10 +989,10 @@
         <v>0.01152435428699405</v>
       </c>
       <c r="B51" t="n">
-        <v>0.01236139024189098</v>
+        <v>0.01236139024189091</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0134475097108454</v>
+        <v>0.01343773173825369</v>
       </c>
     </row>
     <row r="52">
@@ -1000,76 +1000,76 @@
         <v>0.01154581759407946</v>
       </c>
       <c r="B52" t="n">
-        <v>0.01236237503111418</v>
+        <v>0.01236237503111446</v>
       </c>
       <c r="C52" t="n">
-        <v>0.01346199655316569</v>
+        <v>0.01345214035697711</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.01156681300021122</v>
+        <v>0.01156681300021132</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0123632612743663</v>
+        <v>0.01236326127436627</v>
       </c>
       <c r="C53" t="n">
-        <v>0.01347617859689876</v>
+        <v>0.0134662458411544</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.01158735159517835</v>
+        <v>0.01158735159517833</v>
       </c>
       <c r="B54" t="n">
-        <v>0.01236405883899719</v>
+        <v>0.01236405883899742</v>
       </c>
       <c r="C54" t="n">
-        <v>0.01349006258101948</v>
+        <v>0.01348005489100173</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.01160744416483335</v>
+        <v>0.01160744416483309</v>
       </c>
       <c r="B55" t="n">
-        <v>0.01236477660319538</v>
+        <v>0.0123647766031957</v>
       </c>
       <c r="C55" t="n">
-        <v>0.01350365508133189</v>
+        <v>0.01349357404461698</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.01162710120137115</v>
+        <v>0.01162710120137138</v>
       </c>
       <c r="B56" t="n">
-        <v>0.0123654225553661</v>
+        <v>0.01236542255536585</v>
       </c>
       <c r="C56" t="n">
-        <v>0.01351696251504718</v>
+        <v>0.01350680968251803</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.01164633291316929</v>
+        <v>0.01164633291316942</v>
       </c>
       <c r="B57" t="n">
-        <v>0.0123660038834833</v>
+        <v>0.01236600388348335</v>
       </c>
       <c r="C57" t="n">
-        <v>0.01352999114520511</v>
+        <v>0.01351976803203458</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.01166514923420671</v>
+        <v>0.01166514923420656</v>
       </c>
       <c r="B58" t="n">
-        <v>0.01236652705543572</v>
+        <v>0.01236652705543564</v>
       </c>
       <c r="C58" t="n">
-        <v>0.01354274708494652</v>
+        <v>0.01353245517154597</v>
       </c>
     </row>
   </sheetData>
